--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260728.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.69%</t>
+          <t>9.91%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.53%</t>
+          <t>9.58%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>4.85%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>183,678,000</t>
+          <t>109,474,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>109,474,000</t>
+          <t>183,998,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -792,68 +792,68 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>4,935,000</t>
+          <t>346,889,964</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>130,819,945</t>
+          <t>402,425,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>344,689,964</t>
+          <t>4,975,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,374 +865,374 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>398,925,000</t>
+          <t>130,819,945</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>201,517,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>25,514,000</t>
+          <t>145,652,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>200,217,000</t>
+          <t>131,978,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>95,842,442</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>25,764,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>96,642,442</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>80,968,000</t>
+          <t>99,617,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,617,000</t>
+          <t>81,668,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>28,150,000</t>
+          <t>54,837,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>61,590,000</t>
+          <t>28,400,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>54,437,000</t>
+          <t>62,190,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>34,820,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>257,425,590</t>
+          <t>35,070,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>186,406,000</t>
+          <t>259,999,845</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>186,406,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>90,099,080</t>
+          <t>90,799,080</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,443,129,040</t>
+          <t>14,494,667,335</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,304,483,017</t>
+          <t>2,346,616,617</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-14,642,534</t>
+          <t>-134,089,970</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
